--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCategory/2026/202604/Category_P&L_20260430.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCategory/2026/202604/Category_P&L_20260430.xlsx
@@ -42523,28 +42523,28 @@
         <v>46141</v>
       </c>
       <c r="B1109">
-        <v>91094854.09</v>
+        <v>91593172.23</v>
       </c>
       <c r="C1109">
-        <v>-553460.4300000001</v>
+        <v>638525.74</v>
       </c>
       <c r="D1109">
-        <v>-0.006076</v>
+        <v>0.007009</v>
       </c>
       <c r="E1109">
-        <v>-9727.09</v>
+        <v>-99657.87</v>
       </c>
       <c r="F1109">
-        <v>-0.000107</v>
+        <v>-0.001094</v>
       </c>
       <c r="G1109">
-        <v>-90311.41</v>
+        <v>-25267.2</v>
       </c>
       <c r="H1109">
-        <v>-0.0009909999999999999</v>
+        <v>-0.000277</v>
       </c>
       <c r="I1109">
-        <v>-2.64</v>
+        <v>-7.92</v>
       </c>
       <c r="J1109">
         <v>0</v>
@@ -42561,31 +42561,31 @@
         <v>46142</v>
       </c>
       <c r="B1110">
-        <v>91094854.09</v>
+        <v>92671718.28</v>
       </c>
       <c r="C1110">
-        <v>-553460.4300000001</v>
+        <v>915883.26</v>
       </c>
       <c r="D1110">
-        <v>-0.006076</v>
+        <v>0.009998999999999999</v>
       </c>
       <c r="E1110">
-        <v>-9727.09</v>
+        <v>69294.63</v>
       </c>
       <c r="F1110">
-        <v>-0.000107</v>
+        <v>0.000757</v>
       </c>
       <c r="G1110">
-        <v>-90311.41</v>
+        <v>111835.98</v>
       </c>
       <c r="H1110">
-        <v>-0.0009909999999999999</v>
+        <v>0.001221</v>
       </c>
       <c r="I1110">
-        <v>-2.64</v>
+        <v>45.21</v>
       </c>
       <c r="J1110">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K1110">
         <v>0</v>
